--- a/templates/Plan_Proyectos_Template.xlsx
+++ b/templates/Plan_Proyectos_Template.xlsx
@@ -18806,7 +18806,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Bolsas</t>
+          <t>Flor molida</t>
         </is>
       </c>
       <c r="B17" s="32" t="inlineStr">
